--- a/public/menu.xlsx
+++ b/public/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zia Shams\order-system\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00B693D-5CAC-4B2F-8EAB-2456DDB88019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486851F7-1F49-488C-84F9-8AA36191E104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="206">
   <si>
     <t>Category</t>
   </si>
@@ -31,178 +31,613 @@
     <t>Price</t>
   </si>
   <si>
-    <t>Pizza</t>
-  </si>
-  <si>
-    <t>Margherita Pizza</t>
-  </si>
-  <si>
-    <t>Pepperoni Pizza</t>
-  </si>
-  <si>
-    <t>Vegetarian Pizza</t>
-  </si>
-  <si>
-    <t>Hawaiian Pizza</t>
-  </si>
-  <si>
-    <t>BBQ Chicken Pizza</t>
-  </si>
-  <si>
-    <t>Quattro Formaggi</t>
-  </si>
-  <si>
-    <t>Prosciutto &amp; Arugula</t>
-  </si>
-  <si>
-    <t>Spicy Diavola</t>
-  </si>
-  <si>
-    <t>White Pizza</t>
-  </si>
-  <si>
-    <t>Truffle Pizza</t>
-  </si>
-  <si>
-    <t>Pasta</t>
-  </si>
-  <si>
-    <t>Spaghetti Carbonara</t>
-  </si>
-  <si>
-    <t>Fettuccine Alfredo</t>
-  </si>
-  <si>
-    <t>Penne Arrabbiata</t>
-  </si>
-  <si>
-    <t>Lasagna Bolognese</t>
-  </si>
-  <si>
-    <t>Ravioli Ricotta</t>
-  </si>
-  <si>
-    <t>Seafood Linguine</t>
-  </si>
-  <si>
-    <t>Mushroom Risotto</t>
-  </si>
-  <si>
-    <t>Mac and Cheese</t>
-  </si>
-  <si>
-    <t>Veggie Penne</t>
-  </si>
-  <si>
-    <t>Truffle Pasta</t>
-  </si>
-  <si>
-    <t>Salad</t>
-  </si>
-  <si>
-    <t>Caesar Salad</t>
-  </si>
-  <si>
-    <t>Greek Salad</t>
-  </si>
-  <si>
-    <t>Caprese Salad</t>
-  </si>
-  <si>
-    <t>Spinach Salad</t>
-  </si>
-  <si>
-    <t>Arugula Salad</t>
-  </si>
-  <si>
-    <t>Beet Salad</t>
-  </si>
-  <si>
-    <t>Tomato Salad</t>
-  </si>
-  <si>
-    <t>Mozzarella Salad</t>
-  </si>
-  <si>
-    <t>Mixed Green Salad</t>
-  </si>
-  <si>
-    <t>Kale Salad</t>
-  </si>
-  <si>
-    <t>Sides</t>
-  </si>
-  <si>
-    <t>Garlic Bread</t>
-  </si>
-  <si>
-    <t>Mozzarella Sticks</t>
-  </si>
-  <si>
-    <t>Fried Calamari</t>
-  </si>
-  <si>
-    <t>Bruschetta</t>
-  </si>
-  <si>
-    <t>Garlic Knots</t>
-  </si>
-  <si>
-    <t>Chicken Wings</t>
-  </si>
-  <si>
-    <t>Arancini</t>
-  </si>
-  <si>
-    <t>Fried Zucchini</t>
-  </si>
-  <si>
-    <t>Onion Rings</t>
-  </si>
-  <si>
-    <t>Sweet Potato Fries</t>
-  </si>
-  <si>
-    <t>Dessert</t>
-  </si>
-  <si>
-    <t>Tiramisu</t>
-  </si>
-  <si>
-    <t>Chocolate Cake</t>
-  </si>
-  <si>
-    <t>Panna Cotta</t>
-  </si>
-  <si>
-    <t>Cheesecake</t>
-  </si>
-  <si>
-    <t>Cannoli</t>
-  </si>
-  <si>
-    <t>Gelato</t>
-  </si>
-  <si>
-    <t>Zabaglione</t>
-  </si>
-  <si>
-    <t>Panettone</t>
-  </si>
-  <si>
-    <t>Semifreddo</t>
-  </si>
-  <si>
-    <t>Affogato</t>
-  </si>
-  <si>
-    <t>Fish</t>
-  </si>
-  <si>
-    <t>Hilsha Fish 1 KG+</t>
-  </si>
-  <si>
-    <t>Hilsha Fish 2 Pack</t>
+    <t>Koral Fish (Steak - head&amp;tail excluded) - 2lb</t>
+  </si>
+  <si>
+    <t>Shoil Fish Fish (Steak - head&amp;tail excluded) - 2lb</t>
+  </si>
+  <si>
+    <t>Dima Icha (Shrimp with head &amp; Egg) - 250gm</t>
+  </si>
+  <si>
+    <t>Frozen Fish</t>
+  </si>
+  <si>
+    <t>Halal Meat</t>
+  </si>
+  <si>
+    <t>RUI FISH (2KG+) - Full Fish Cut</t>
+  </si>
+  <si>
+    <t>Rui Fish 3KG+ (Full Fish Cut &amp; Desclaed)</t>
+  </si>
+  <si>
+    <t>Ayer Fish (1.5KG+) - Full Fish Cut</t>
+  </si>
+  <si>
+    <t>Boal Fish (2KG+) - Full Fish Cut</t>
+  </si>
+  <si>
+    <t>Chitol Fish (2/3KG) - Full Fish Cut</t>
+  </si>
+  <si>
+    <t>Mrigel 3KG+ (Full Fishs Cut &amp; Desclaed)</t>
+  </si>
+  <si>
+    <t>Hilsha Fish 1000gm++ - Full Fish Cut</t>
+  </si>
+  <si>
+    <t>Hilsha Egg (200gm Pack)</t>
+  </si>
+  <si>
+    <t>Tengra 500gm Pack</t>
+  </si>
+  <si>
+    <t>Pangash 2K+ - Full Fish Cut</t>
+  </si>
+  <si>
+    <t>Magur Fish (Steak Only) - 800gm Pack</t>
+  </si>
+  <si>
+    <t>Bula Icha 250gm Pack</t>
+  </si>
+  <si>
+    <t>Silver Pomfret - Large (Approx 1lb) - Full Fish</t>
+  </si>
+  <si>
+    <t>Koi Fish 250gm Pack</t>
+  </si>
+  <si>
+    <t>Koi Fish 1KG Pack</t>
+  </si>
+  <si>
+    <t>Keski Fish 250gm Pack</t>
+  </si>
+  <si>
+    <t>Mola Fish (মৌড়ালা মাছ) 250gm Pack</t>
+  </si>
+  <si>
+    <t>Mola Fish (মৌড়ালা মাছ) 500gm Pack</t>
+  </si>
+  <si>
+    <t>Kajuli Fish 500gm Pack</t>
+  </si>
+  <si>
+    <t>Pabda Fish 500gm Pack</t>
+  </si>
+  <si>
+    <t>Star Baim 500gm Pack</t>
+  </si>
+  <si>
+    <t>Shing Fish 500gm Pack</t>
+  </si>
+  <si>
+    <t>Baila Fish 500gm Pack</t>
+  </si>
+  <si>
+    <t>Local Beef (approx. 2.5lb pack) - Price is per LB</t>
+  </si>
+  <si>
+    <t>Boneless Beef (approx. 2.5lb pack) - Price is per LB</t>
+  </si>
+  <si>
+    <t>Beef liver (approx. 2lb pack) - Price is per LB</t>
+  </si>
+  <si>
+    <t>Beef Lung - Price is per LB</t>
+  </si>
+  <si>
+    <t>Beef Kidney - Price is per LB</t>
+  </si>
+  <si>
+    <t>Ground Beef (approx. 1lb Pack) - Price is per LB</t>
+  </si>
+  <si>
+    <t>Beef Nalli (3/4lb Pack) - Price is per LB</t>
+  </si>
+  <si>
+    <t>Small Hard chicken - Price is per chicken</t>
+  </si>
+  <si>
+    <t>Yellow Chicken (clean &amp; cut) - Price is per chicken</t>
+  </si>
+  <si>
+    <t>Free Run Red Chicken (clean &amp; Whole)- Price is per chicken</t>
+  </si>
+  <si>
+    <t>Duck (Regular) - Cut &amp; Skin Burned - Price is per duck</t>
+  </si>
+  <si>
+    <t>Mutton (Goat) - Approx. 2lb Pack - Local - Price is per LB</t>
+  </si>
+  <si>
+    <t>Local Lamb (2lb Pack) - Price is per LB</t>
+  </si>
+  <si>
+    <t>Lamb Leg - (whole) - Local - Price is per LB</t>
+  </si>
+  <si>
+    <t>Lamb Chop - Price is per LB</t>
+  </si>
+  <si>
+    <t>Nona Ilish (whole fish)</t>
+  </si>
+  <si>
+    <t>Loita Shutki 150gm</t>
+  </si>
+  <si>
+    <t>Keski Shutki 150gm</t>
+  </si>
+  <si>
+    <t>Dried Fish</t>
+  </si>
+  <si>
+    <t>Chepa Shutki 150gm</t>
+  </si>
+  <si>
+    <t>Faisha Shidol 150gm</t>
+  </si>
+  <si>
+    <t>Premium Sweets Morog Pulao</t>
+  </si>
+  <si>
+    <t>Premium sweets Brain Masala</t>
+  </si>
+  <si>
+    <t>Loita Shutki Bhorta</t>
+  </si>
+  <si>
+    <t>Chepa Bhorta 200gm</t>
+  </si>
+  <si>
+    <t>Kothbel Bhorta 200gm</t>
+  </si>
+  <si>
+    <t>Taki Vorta</t>
+  </si>
+  <si>
+    <t>Jolpai Vorta 200gm</t>
+  </si>
+  <si>
+    <t>Ready to Eat</t>
+  </si>
+  <si>
+    <t>PLAIN PARATHA 30PACK</t>
+  </si>
+  <si>
+    <t>Naga Singara</t>
+  </si>
+  <si>
+    <t>Vegetable Singara Family Pack (25 Pieces)</t>
+  </si>
+  <si>
+    <t>Vegetable Samosa</t>
+  </si>
+  <si>
+    <t>Dalpuri</t>
+  </si>
+  <si>
+    <t>Alupuri</t>
+  </si>
+  <si>
+    <t>Frozen Snacks</t>
+  </si>
+  <si>
+    <t>Bangladeshi Frozen Seem</t>
+  </si>
+  <si>
+    <t>Bangladeshi Frozen Potol</t>
+  </si>
+  <si>
+    <t>Frozen Chui Jhal</t>
+  </si>
+  <si>
+    <t>Lal Shak</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Frozen Jolpai</t>
+  </si>
+  <si>
+    <t>Dal er bori 300gm</t>
+  </si>
+  <si>
+    <t>Frozen Satkora</t>
+  </si>
+  <si>
+    <t>Kochur Loti</t>
+  </si>
+  <si>
+    <t>Frozen Vegetables</t>
+  </si>
+  <si>
+    <t>Kalijeera rice 9lb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chinigura Rice 9lb </t>
+  </si>
+  <si>
+    <t>Long Grain Parboiled 8KG</t>
+  </si>
+  <si>
+    <t>Kataribhog Rice 5KG</t>
+  </si>
+  <si>
+    <t>Kalo Chola 4lb</t>
+  </si>
+  <si>
+    <t>MOONG DAL 4LB</t>
+  </si>
+  <si>
+    <t>Cholar Dal (ছোলার ডাল) - 4LB</t>
+  </si>
+  <si>
+    <t>Yellow Peas (চটপটির ডাবলি বুট)</t>
+  </si>
+  <si>
+    <t>Rice &amp; Grains</t>
+  </si>
+  <si>
+    <t>Nicobena Naga Pickle</t>
+  </si>
+  <si>
+    <t>Ruchi Chalta Pickle</t>
+  </si>
+  <si>
+    <t>Ruchi Boroi Tetul Mix Pickle</t>
+  </si>
+  <si>
+    <t>Ruchi Olive Pickle</t>
+  </si>
+  <si>
+    <t>Nicobena Mix Pickle</t>
+  </si>
+  <si>
+    <t>Nicobena Mango Pickle</t>
+  </si>
+  <si>
+    <t>Nicobina Tetul Pickle</t>
+  </si>
+  <si>
+    <t>Nicobina Garlic Pickle 220gm</t>
+  </si>
+  <si>
+    <t>Pickle &amp; Chutney</t>
+  </si>
+  <si>
+    <t>Laccha Semai 200gm</t>
+  </si>
+  <si>
+    <t>Bombay Laccha Semai 350gm</t>
+  </si>
+  <si>
+    <t>Ispahani/Taza Tea 400gm</t>
+  </si>
+  <si>
+    <t>Nido Milk Powder 2500gm</t>
+  </si>
+  <si>
+    <t>Nido Milk Powder 400gm</t>
+  </si>
+  <si>
+    <t>Rooh Afza (800 ml)</t>
+  </si>
+  <si>
+    <t>Tetul Paste</t>
+  </si>
+  <si>
+    <t>ACI Stick Noodles 180gm</t>
+  </si>
+  <si>
+    <t>Nurjahan Paan Masala</t>
+  </si>
+  <si>
+    <t>Semai</t>
+  </si>
+  <si>
+    <t>Tokma Seed (তোকমা দানা)</t>
+  </si>
+  <si>
+    <t>Besan (4lb)</t>
+  </si>
+  <si>
+    <t>Sooji (4lb)</t>
+  </si>
+  <si>
+    <t>Sac Biriyani Essence</t>
+  </si>
+  <si>
+    <t>Food Color (Red) (25gm)</t>
+  </si>
+  <si>
+    <t>Food Color (Yellow) (25gm)</t>
+  </si>
+  <si>
+    <t>Khejur Gur 1KG</t>
+  </si>
+  <si>
+    <t>Radhuni Kashundi</t>
+  </si>
+  <si>
+    <t>Fuchka - Ready to Fry (200gm)</t>
+  </si>
+  <si>
+    <t>Fried Onion (পেয়াজ বেরেস্তা)</t>
+  </si>
+  <si>
+    <t>Deshi Alubukhara 396gm</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>ACI Regular Toast</t>
+  </si>
+  <si>
+    <t>Banaful Plain Toast</t>
+  </si>
+  <si>
+    <t>Olympia Ghee Toast</t>
+  </si>
+  <si>
+    <t>Kishwan Mango Bar</t>
+  </si>
+  <si>
+    <t>Pineapple Cream Biscuit</t>
+  </si>
+  <si>
+    <t>PUFFED RICE</t>
+  </si>
+  <si>
+    <t>Flattened Rice - Chira (4lb)</t>
+  </si>
+  <si>
+    <t>Muri Moa (Jar)</t>
+  </si>
+  <si>
+    <t>Bombay Chanachur (Regular)</t>
+  </si>
+  <si>
+    <t>Ruchi Hot Chanachur 300gm</t>
+  </si>
+  <si>
+    <t>Ruchi BBQ Chanachur 300gm</t>
+  </si>
+  <si>
+    <t>Dry Cake</t>
+  </si>
+  <si>
+    <t>Energy Biscuit</t>
+  </si>
+  <si>
+    <t>Moong dal bhaja (dalmuth)</t>
+  </si>
+  <si>
+    <t>Dry Snack</t>
+  </si>
+  <si>
+    <t>Garlic Paste (750ML) - রসুন বাটা</t>
+  </si>
+  <si>
+    <t>Ginger Paste (750ML) - আদা বাটা</t>
+  </si>
+  <si>
+    <t>Ginger Garlic Paste (750ml)</t>
+  </si>
+  <si>
+    <t>RADHUNI CHILI POWDER (400GM)</t>
+  </si>
+  <si>
+    <t>RADHUNI CHILI POWDER (500GM)</t>
+  </si>
+  <si>
+    <t>KASHMIRI CHILI POWDER 400GM</t>
+  </si>
+  <si>
+    <t>Desi Crushed Chilli (Hot) - 400gm</t>
+  </si>
+  <si>
+    <t>CORIANDER 500GM - ধনে গুড়া</t>
+  </si>
+  <si>
+    <t>CUMIN POWDER 200GM - জিরা গুড়া</t>
+  </si>
+  <si>
+    <t>CUMIN POWDER 500GM - জিরা গুড়া</t>
+  </si>
+  <si>
+    <t>TURMERIC POWDER 200gm - হলুদ গুড়া</t>
+  </si>
+  <si>
+    <t>RADHUNI GARAM MASALA</t>
+  </si>
+  <si>
+    <t>MUSTARD SEED POWDER (200GM) - সর্ষে গুড়ো</t>
+  </si>
+  <si>
+    <t>White Pepper Powder (100mg) - সাদা গোল মরিচ গূড়ো</t>
+  </si>
+  <si>
+    <t>Radhuni Bhuna Khichuri Mix</t>
+  </si>
+  <si>
+    <t>RADHUNI PACHFORON POWDER</t>
+  </si>
+  <si>
+    <t>RADHUNI BEEF CURRY</t>
+  </si>
+  <si>
+    <t>RADHUNI CHATPATI</t>
+  </si>
+  <si>
+    <t>RADHUNI CHICKEN MASALA</t>
+  </si>
+  <si>
+    <t>RADHUNI MEJBANI MASALA</t>
+  </si>
+  <si>
+    <t>RADHUNI HYDRABADI BIRIYANI</t>
+  </si>
+  <si>
+    <t>RADHUNI REZALA</t>
+  </si>
+  <si>
+    <t>Radhuni Halim Mix</t>
+  </si>
+  <si>
+    <t>ACI KABAB MASASLA</t>
+  </si>
+  <si>
+    <t>RADHUNI BORHANI</t>
+  </si>
+  <si>
+    <t>BOMBAY BORHANI</t>
+  </si>
+  <si>
+    <t>RADHUNI TEHARI MASALA</t>
+  </si>
+  <si>
+    <t>RADHUNI BIRIYANI</t>
+  </si>
+  <si>
+    <t>RADHUNI KALABHUNA</t>
+  </si>
+  <si>
+    <t>ACI Shahi Roast Masala</t>
+  </si>
+  <si>
+    <t>Radhuni Roast Masala</t>
+  </si>
+  <si>
+    <t>ACI chicken Tandoori Masala</t>
+  </si>
+  <si>
+    <t>ACI Tehari Masala</t>
+  </si>
+  <si>
+    <t>Jaifol Powder (100 gm) - জয়ফল গুড়ো</t>
+  </si>
+  <si>
+    <t>Javitri Powder (50gm) - জয়ত্রি গুড়ো</t>
+  </si>
+  <si>
+    <t>Radhuni Shorshe Ilish Masala</t>
+  </si>
+  <si>
+    <t>Radhuni Fish Curry Masala</t>
+  </si>
+  <si>
+    <t>Radhuni Korma Masala</t>
+  </si>
+  <si>
+    <t>Spice Powder &amp; Paste</t>
+  </si>
+  <si>
+    <t>GREEN CARDAMOM (100GM) - এলাচ</t>
+  </si>
+  <si>
+    <t>CLOVE WHOLE (100GM) - লবঙ্গ</t>
+  </si>
+  <si>
+    <t>FENNEL SEED (মৌরী)</t>
+  </si>
+  <si>
+    <t>CORIANDER SEED (আস্তো ধনিয়া) 300gm</t>
+  </si>
+  <si>
+    <t>CINNAMON STICK (200GM) - দারুচিনি</t>
+  </si>
+  <si>
+    <t>RADHUNI DRY CHILI WHOLE (100GM)</t>
+  </si>
+  <si>
+    <t>RADHUNI BAYLEAF - তেজপাতা</t>
+  </si>
+  <si>
+    <t>Ajwain Seed 200gm - জোয়াইন</t>
+  </si>
+  <si>
+    <t>Kalijira 200 gm - কালিজিরা</t>
+  </si>
+  <si>
+    <t>Black Cardamom 100gm - কালো এলাচ</t>
+  </si>
+  <si>
+    <t>Fenugreek Seed (Methi) - 200gm</t>
+  </si>
+  <si>
+    <t>Cumin Seed (Whole) - 200gm</t>
+  </si>
+  <si>
+    <t>Radhuni Seed 100gm</t>
+  </si>
+  <si>
+    <t>Popy Seed (দেশী সাদা পোস্ত দানা) - 100gm</t>
+  </si>
+  <si>
+    <t>Black Pepper (Whole) - 50gm</t>
+  </si>
+  <si>
+    <t>Nutmeg (Whole) - 50gm</t>
+  </si>
+  <si>
+    <t>Shah Jeera</t>
+  </si>
+  <si>
+    <t>Kabab Chini</t>
+  </si>
+  <si>
+    <t>Whole Pachforon</t>
+  </si>
+  <si>
+    <t>Whole Garam Masala 100gm</t>
+  </si>
+  <si>
+    <t>Star Anis 100gm</t>
+  </si>
+  <si>
+    <t>Javitri Whole (50gm) - জয়ত্রি</t>
+  </si>
+  <si>
+    <t>Whole Spices</t>
+  </si>
+  <si>
+    <t>Kalojam 800gm</t>
+  </si>
+  <si>
+    <t>Roshmalai (Comilla) 800gm</t>
+  </si>
+  <si>
+    <t>Muktagasar Monda 800gm</t>
+  </si>
+  <si>
+    <t>Chanamukhi 500gm</t>
+  </si>
+  <si>
+    <t>Deshi Sweets</t>
+  </si>
+  <si>
+    <t>Radhuni Jorda Mix</t>
+  </si>
+  <si>
+    <t>Radhuni Faluda Mix</t>
+  </si>
+  <si>
+    <t>Banaful Shon papri 200gm</t>
+  </si>
+  <si>
+    <t>ACI Khir Mix</t>
+  </si>
+  <si>
+    <t>Radhuni Firni Mix</t>
+  </si>
+  <si>
+    <t>Mango Pulp</t>
+  </si>
+  <si>
+    <t>Desert Ingredients</t>
   </si>
 </sst>
 </file>
@@ -241,7 +676,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -275,11 +710,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -296,6 +779,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,11 +1089,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C191"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -619,120 +1110,120 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3">
-        <v>12.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>14.99</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3">
-        <v>13.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3">
-        <v>15.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3">
-        <v>15.99</v>
+        <v>54.99</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3">
-        <v>16.989999999999998</v>
+        <v>48.99</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3">
-        <v>16.989999999999998</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3">
-        <v>15.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3">
-        <v>14.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3">
-        <v>18.989999999999998</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3">
         <v>13.99</v>
@@ -740,373 +1231,373 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C13" s="3">
-        <v>12.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C14" s="3">
-        <v>11.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3">
-        <v>14.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="3">
-        <v>13.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="3">
-        <v>16.989999999999998</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="3">
-        <v>13.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="3">
-        <v>11.99</v>
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="3">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3">
-        <v>17.989999999999998</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C22" s="3">
-        <v>9.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="3">
-        <v>10.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="3">
-        <v>11.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="3">
-        <v>9.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="3">
-        <v>10.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="3">
-        <v>10.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="3">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="3">
-        <v>11.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="3">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="3">
-        <v>10.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C32" s="3">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="C33" s="3">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C34" s="3">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C35" s="3">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C36" s="3">
-        <v>6.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C37" s="3">
-        <v>10.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3">
-        <v>8.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C39" s="3">
-        <v>7.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="3">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C41" s="3">
-        <v>7.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C42" s="3">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C43" s="3">
-        <v>7.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C44" s="3">
-        <v>6.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C45" s="3">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="C46" s="3">
         <v>5.99</v>
@@ -1114,79 +1605,1597 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C47" s="3">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C48" s="3">
-        <v>6.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C49" s="3">
-        <v>7.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C50" s="3">
-        <v>6.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="3">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="5">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C53" s="5">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63">
         <v>5.99</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="5">
-        <v>37.99</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53" s="5">
-        <v>19.989999999999998</v>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B64" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B65" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B66" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" s="7">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71" s="7">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="7">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C73" s="7">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" s="7">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C75" s="7">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" s="7">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C77" s="9">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B78" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B79" t="s">
+        <v>87</v>
+      </c>
+      <c r="C79">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B81" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B84" t="s">
+        <v>92</v>
+      </c>
+      <c r="C84">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B85" t="s">
+        <v>93</v>
+      </c>
+      <c r="C85">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B86" t="s">
+        <v>95</v>
+      </c>
+      <c r="C86">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B87" t="s">
+        <v>96</v>
+      </c>
+      <c r="C87">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B88" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B89" t="s">
+        <v>98</v>
+      </c>
+      <c r="C89">
+        <v>84.99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B90" t="s">
+        <v>99</v>
+      </c>
+      <c r="C90">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B91" t="s">
+        <v>100</v>
+      </c>
+      <c r="C91">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B92" t="s">
+        <v>101</v>
+      </c>
+      <c r="C92">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B93" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93">
+        <v>2.4900000000000002</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B94" t="s">
+        <v>103</v>
+      </c>
+      <c r="C94">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B95" t="s">
+        <v>104</v>
+      </c>
+      <c r="C95">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B96" t="s">
+        <v>105</v>
+      </c>
+      <c r="C96">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B97" t="s">
+        <v>106</v>
+      </c>
+      <c r="C97">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B98" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B99" t="s">
+        <v>108</v>
+      </c>
+      <c r="C99">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B100" t="s">
+        <v>109</v>
+      </c>
+      <c r="C100">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B101" t="s">
+        <v>110</v>
+      </c>
+      <c r="C101">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B102" t="s">
+        <v>111</v>
+      </c>
+      <c r="C102">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B103" t="s">
+        <v>112</v>
+      </c>
+      <c r="C103">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B104" t="s">
+        <v>113</v>
+      </c>
+      <c r="C104">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B105" t="s">
+        <v>114</v>
+      </c>
+      <c r="C105">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B106" t="s">
+        <v>115</v>
+      </c>
+      <c r="C106">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B107" t="s">
+        <v>117</v>
+      </c>
+      <c r="C107">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B108" t="s">
+        <v>118</v>
+      </c>
+      <c r="C108">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B109" t="s">
+        <v>119</v>
+      </c>
+      <c r="C109">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B110" t="s">
+        <v>120</v>
+      </c>
+      <c r="C110">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B111" t="s">
+        <v>121</v>
+      </c>
+      <c r="C111">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B112" t="s">
+        <v>122</v>
+      </c>
+      <c r="C112">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B113" t="s">
+        <v>123</v>
+      </c>
+      <c r="C113">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B114" t="s">
+        <v>124</v>
+      </c>
+      <c r="C114">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B115" t="s">
+        <v>125</v>
+      </c>
+      <c r="C115">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B116" t="s">
+        <v>126</v>
+      </c>
+      <c r="C116">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B117" t="s">
+        <v>127</v>
+      </c>
+      <c r="C117">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B118" t="s">
+        <v>128</v>
+      </c>
+      <c r="C118">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B119" t="s">
+        <v>129</v>
+      </c>
+      <c r="C119">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C120">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B121" t="s">
+        <v>132</v>
+      </c>
+      <c r="C121">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B122" t="s">
+        <v>133</v>
+      </c>
+      <c r="C122">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B123" t="s">
+        <v>134</v>
+      </c>
+      <c r="C123">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B124" t="s">
+        <v>135</v>
+      </c>
+      <c r="C124">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B125" t="s">
+        <v>136</v>
+      </c>
+      <c r="C125">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B126" t="s">
+        <v>137</v>
+      </c>
+      <c r="C126">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B127" t="s">
+        <v>138</v>
+      </c>
+      <c r="C127">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B128" t="s">
+        <v>139</v>
+      </c>
+      <c r="C128">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B129" t="s">
+        <v>140</v>
+      </c>
+      <c r="C129">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B130" t="s">
+        <v>141</v>
+      </c>
+      <c r="C130">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B131" t="s">
+        <v>142</v>
+      </c>
+      <c r="C131">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B132" t="s">
+        <v>143</v>
+      </c>
+      <c r="C132">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B133" t="s">
+        <v>144</v>
+      </c>
+      <c r="C133">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B134" t="s">
+        <v>145</v>
+      </c>
+      <c r="C134">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B135" t="s">
+        <v>146</v>
+      </c>
+      <c r="C135">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B136" t="s">
+        <v>147</v>
+      </c>
+      <c r="C136">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B137" t="s">
+        <v>148</v>
+      </c>
+      <c r="C137">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B138" t="s">
+        <v>149</v>
+      </c>
+      <c r="C138">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B139" t="s">
+        <v>150</v>
+      </c>
+      <c r="C139">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B140" t="s">
+        <v>151</v>
+      </c>
+      <c r="C140">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B141" t="s">
+        <v>151</v>
+      </c>
+      <c r="C141">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B142" t="s">
+        <v>152</v>
+      </c>
+      <c r="C142">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B143" t="s">
+        <v>153</v>
+      </c>
+      <c r="C143">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B144" t="s">
+        <v>154</v>
+      </c>
+      <c r="C144">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B145" t="s">
+        <v>155</v>
+      </c>
+      <c r="C145">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B146" t="s">
+        <v>156</v>
+      </c>
+      <c r="C146">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B147" t="s">
+        <v>157</v>
+      </c>
+      <c r="C147">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B148" t="s">
+        <v>158</v>
+      </c>
+      <c r="C148">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B149" t="s">
+        <v>159</v>
+      </c>
+      <c r="C149">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B150" t="s">
+        <v>160</v>
+      </c>
+      <c r="C150">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B151" t="s">
+        <v>161</v>
+      </c>
+      <c r="C151">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B152" t="s">
+        <v>162</v>
+      </c>
+      <c r="C152">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B153" t="s">
+        <v>163</v>
+      </c>
+      <c r="C153">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B154" t="s">
+        <v>164</v>
+      </c>
+      <c r="C154">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B155" t="s">
+        <v>165</v>
+      </c>
+      <c r="C155">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B156" t="s">
+        <v>166</v>
+      </c>
+      <c r="C156">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B157" t="s">
+        <v>167</v>
+      </c>
+      <c r="C157">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B158" t="s">
+        <v>168</v>
+      </c>
+      <c r="C158">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B159" t="s">
+        <v>169</v>
+      </c>
+      <c r="C159">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B160" t="s">
+        <v>171</v>
+      </c>
+      <c r="C160">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B161" t="s">
+        <v>172</v>
+      </c>
+      <c r="C161">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B162" t="s">
+        <v>173</v>
+      </c>
+      <c r="C162">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B163" t="s">
+        <v>174</v>
+      </c>
+      <c r="C163">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B164" t="s">
+        <v>175</v>
+      </c>
+      <c r="C164">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B165" t="s">
+        <v>176</v>
+      </c>
+      <c r="C165">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B166" t="s">
+        <v>177</v>
+      </c>
+      <c r="C166">
+        <v>2.4900000000000002</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B167" t="s">
+        <v>178</v>
+      </c>
+      <c r="C167">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B168" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B169" t="s">
+        <v>180</v>
+      </c>
+      <c r="C169">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B170" t="s">
+        <v>181</v>
+      </c>
+      <c r="C170">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B171" t="s">
+        <v>182</v>
+      </c>
+      <c r="C171">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B172" t="s">
+        <v>183</v>
+      </c>
+      <c r="C172">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B173" t="s">
+        <v>184</v>
+      </c>
+      <c r="C173">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B174" t="s">
+        <v>185</v>
+      </c>
+      <c r="C174">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B175" t="s">
+        <v>186</v>
+      </c>
+      <c r="C175">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B176" t="s">
+        <v>187</v>
+      </c>
+      <c r="C176">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B177" t="s">
+        <v>188</v>
+      </c>
+      <c r="C177">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B178" t="s">
+        <v>189</v>
+      </c>
+      <c r="C178">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B179" t="s">
+        <v>190</v>
+      </c>
+      <c r="C179">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B180" t="s">
+        <v>191</v>
+      </c>
+      <c r="C180">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B181" t="s">
+        <v>192</v>
+      </c>
+      <c r="C181">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B182" t="s">
+        <v>194</v>
+      </c>
+      <c r="C182">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B183" t="s">
+        <v>195</v>
+      </c>
+      <c r="C183">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B184" t="s">
+        <v>196</v>
+      </c>
+      <c r="C184">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B185" t="s">
+        <v>197</v>
+      </c>
+      <c r="C185">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B186" t="s">
+        <v>199</v>
+      </c>
+      <c r="C186">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B187" t="s">
+        <v>200</v>
+      </c>
+      <c r="C187">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B188" t="s">
+        <v>201</v>
+      </c>
+      <c r="C188">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B189" t="s">
+        <v>202</v>
+      </c>
+      <c r="C189">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B190" t="s">
+        <v>203</v>
+      </c>
+      <c r="C190">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B191" t="s">
+        <v>204</v>
+      </c>
+      <c r="C191">
+        <v>6.99</v>
       </c>
     </row>
   </sheetData>

--- a/public/menu.xlsx
+++ b/public/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zia Shams\order-system\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486851F7-1F49-488C-84F9-8AA36191E104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995436AB-2637-4E85-A5F1-437A79F08C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="208">
   <si>
     <t>Category</t>
   </si>
@@ -638,6 +638,12 @@
   </si>
   <si>
     <t>Desert Ingredients</t>
+  </si>
+  <si>
+    <t>Specials</t>
+  </si>
+  <si>
+    <t>Sale Price</t>
   </si>
 </sst>
 </file>
@@ -676,7 +682,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -758,11 +764,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -787,6 +806,13 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1089,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C191"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1097,7 +1123,7 @@
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1107,170 +1133,185 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="12">
+        <v>10.99</v>
+      </c>
+      <c r="D2" s="12">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="12">
+        <v>84.99</v>
+      </c>
+      <c r="D3" s="12">
+        <v>79.989999999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3">
+        <v>13.99</v>
+      </c>
+      <c r="D4" s="12">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5.99</v>
+      </c>
+      <c r="D5" s="12">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C6" s="11">
         <v>24.99</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3">
-        <v>42.99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3">
-        <v>54.99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3">
-        <v>48.99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>42.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3">
-        <v>37.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>54.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>48.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3">
-        <v>5.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1278,10 +1319,10 @@
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C17" s="3">
-        <v>13.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -1289,10 +1330,10 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C18" s="3">
-        <v>6.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -1300,10 +1341,10 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C19" s="3">
-        <v>18.989999999999998</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1311,7 +1352,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C20" s="3">
         <v>5.99</v>
@@ -1322,10 +1363,10 @@
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C21" s="3">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1333,10 +1374,10 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C22" s="3">
-        <v>11.99</v>
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1344,10 +1385,10 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C23" s="3">
-        <v>15.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -1355,10 +1396,10 @@
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C24" s="3">
-        <v>12.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -1366,10 +1407,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C25" s="3">
-        <v>12.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -1377,10 +1418,10 @@
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C26" s="3">
-        <v>12.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -1388,7 +1429,7 @@
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C27" s="3">
         <v>12.99</v>
@@ -1396,35 +1437,35 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C28" s="3">
-        <v>7.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C29" s="3">
-        <v>10.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C30" s="3">
-        <v>6.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -1432,10 +1473,10 @@
         <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C31" s="3">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -1443,10 +1484,10 @@
         <v>7</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C32" s="3">
-        <v>6.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -1454,7 +1495,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C33" s="3">
         <v>6.99</v>
@@ -1465,10 +1506,10 @@
         <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C34" s="3">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -1476,7 +1517,7 @@
         <v>7</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C35" s="3">
         <v>6.99</v>
@@ -1487,10 +1528,10 @@
         <v>7</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C36" s="3">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1498,10 +1539,10 @@
         <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C37" s="3">
-        <v>15.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1509,10 +1550,10 @@
         <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C38" s="3">
-        <v>34.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1520,10 +1561,10 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C39" s="3">
-        <v>13.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -1531,10 +1572,10 @@
         <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C40" s="3">
-        <v>11.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -1542,10 +1583,10 @@
         <v>7</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3">
-        <v>11.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -1553,43 +1594,43 @@
         <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C42" s="3">
-        <v>11.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C43" s="3">
-        <v>16.989999999999998</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C44" s="3">
-        <v>6.49</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C45" s="3">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -1597,10 +1638,10 @@
         <v>49</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="3">
-        <v>5.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -1608,43 +1649,43 @@
         <v>49</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C47" s="3">
-        <v>5.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" s="3">
-        <v>15.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C49" s="3">
-        <v>15.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C50" s="3">
-        <v>6.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -1652,31 +1693,31 @@
         <v>59</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C51" s="3">
-        <v>6.49</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C52" s="5">
-        <v>6.49</v>
+      <c r="B52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="3">
+        <v>15.99</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53" s="5">
+      <c r="B53" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="3">
         <v>6.49</v>
       </c>
     </row>
@@ -1684,63 +1725,57 @@
       <c r="A54" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="3">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="5">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" s="5">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" t="s">
         <v>58</v>
       </c>
-      <c r="C54">
+      <c r="C57">
         <v>3.99</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57">
-        <v>11.99</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B58" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58">
-        <v>4.99</v>
-      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C59">
         <v>4.99</v>
@@ -1751,43 +1786,43 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C60">
-        <v>4.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C61">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C62">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C63">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -1795,7 +1830,7 @@
         <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C64">
         <v>3.99</v>
@@ -1806,7 +1841,7 @@
         <v>76</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C65">
         <v>3.99</v>
@@ -1817,10 +1852,10 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C66">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -1828,10 +1863,10 @@
         <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C67">
-        <v>7.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1839,7 +1874,7 @@
         <v>76</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C68">
         <v>3.99</v>
@@ -1850,7 +1885,7 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C69">
         <v>3.99</v>
@@ -1858,35 +1893,35 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C70" s="7">
-        <v>26.99</v>
+        <v>76</v>
+      </c>
+      <c r="B70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70">
+        <v>7.99</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C71" s="7">
-        <v>26.99</v>
+        <v>76</v>
+      </c>
+      <c r="B71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71">
+        <v>3.99</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C72" s="7">
-        <v>16.989999999999998</v>
+        <v>76</v>
+      </c>
+      <c r="B72" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72">
+        <v>3.99</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1894,10 +1929,10 @@
         <v>85</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C73" s="7">
-        <v>22.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -1905,10 +1940,10 @@
         <v>85</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C74" s="7">
-        <v>6.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -1916,10 +1951,10 @@
         <v>85</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C75" s="7">
-        <v>8.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -1927,54 +1962,54 @@
         <v>85</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C76" s="7">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" s="9">
-        <v>6.49</v>
+      <c r="B77" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" s="7">
+        <v>6.99</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B78" t="s">
-        <v>86</v>
-      </c>
-      <c r="C78">
-        <v>6.99</v>
+        <v>85</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C78" s="7">
+        <v>8.99</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B79" t="s">
-        <v>87</v>
-      </c>
-      <c r="C79">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="7">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B80" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80">
-        <v>4.99</v>
+        <v>85</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C80" s="9">
+        <v>6.49</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -1982,10 +2017,10 @@
         <v>94</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C81">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -1993,7 +2028,7 @@
         <v>94</v>
       </c>
       <c r="B82" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C82">
         <v>4.99</v>
@@ -2004,7 +2039,7 @@
         <v>94</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C83">
         <v>4.99</v>
@@ -2015,10 +2050,10 @@
         <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C84">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -2026,43 +2061,43 @@
         <v>94</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C85">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C86">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C87">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C88">
-        <v>9.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -2070,10 +2105,10 @@
         <v>116</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C89">
-        <v>84.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -2081,10 +2116,10 @@
         <v>116</v>
       </c>
       <c r="B90" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C90">
-        <v>17.989999999999998</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -2092,10 +2127,10 @@
         <v>116</v>
       </c>
       <c r="B91" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C91">
-        <v>6.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -2103,10 +2138,10 @@
         <v>116</v>
       </c>
       <c r="B92" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C92">
-        <v>4.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -2114,10 +2149,10 @@
         <v>116</v>
       </c>
       <c r="B93" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C93">
-        <v>2.4900000000000002</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -2125,7 +2160,7 @@
         <v>116</v>
       </c>
       <c r="B94" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C94">
         <v>4.99</v>
@@ -2136,10 +2171,10 @@
         <v>116</v>
       </c>
       <c r="B95" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C95">
-        <v>1.99</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -2147,10 +2182,10 @@
         <v>116</v>
       </c>
       <c r="B96" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C96">
-        <v>2.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -2158,10 +2193,10 @@
         <v>116</v>
       </c>
       <c r="B97" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C97">
-        <v>7.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -2169,10 +2204,10 @@
         <v>116</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C98">
-        <v>6.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -2180,10 +2215,10 @@
         <v>116</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C99">
-        <v>1.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -2191,10 +2226,10 @@
         <v>116</v>
       </c>
       <c r="B100" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C100">
-        <v>1.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -2202,7 +2237,7 @@
         <v>116</v>
       </c>
       <c r="B101" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C101">
         <v>1.99</v>
@@ -2213,10 +2248,10 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C102">
-        <v>15.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -2224,10 +2259,10 @@
         <v>116</v>
       </c>
       <c r="B103" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C103">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -2235,10 +2270,10 @@
         <v>116</v>
       </c>
       <c r="B104" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C104">
-        <v>5.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -2246,10 +2281,10 @@
         <v>116</v>
       </c>
       <c r="B105" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C105">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -2257,32 +2292,32 @@
         <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C106">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B107" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C107">
-        <v>4.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B108" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C108">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -2290,10 +2325,10 @@
         <v>131</v>
       </c>
       <c r="B109" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C109">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -2301,10 +2336,10 @@
         <v>131</v>
       </c>
       <c r="B110" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C110">
-        <v>0.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -2312,10 +2347,10 @@
         <v>131</v>
       </c>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C111">
-        <v>1.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -2323,10 +2358,10 @@
         <v>131</v>
       </c>
       <c r="B112" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C112">
-        <v>3.99</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -2334,10 +2369,10 @@
         <v>131</v>
       </c>
       <c r="B113" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C113">
-        <v>5.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -2345,10 +2380,10 @@
         <v>131</v>
       </c>
       <c r="B114" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C114">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -2356,10 +2391,10 @@
         <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C115">
-        <v>4.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -2367,10 +2402,10 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C116">
-        <v>4.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -2378,7 +2413,7 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C117">
         <v>4.49</v>
@@ -2389,10 +2424,10 @@
         <v>131</v>
       </c>
       <c r="B118" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C118">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -2400,10 +2435,10 @@
         <v>131</v>
       </c>
       <c r="B119" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C119">
-        <v>3.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -2411,32 +2446,32 @@
         <v>131</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C120">
-        <v>0.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C121">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="B122" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C122">
-        <v>6.99</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -2444,7 +2479,7 @@
         <v>170</v>
       </c>
       <c r="B123" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C123">
         <v>6.99</v>
@@ -2455,7 +2490,7 @@
         <v>170</v>
       </c>
       <c r="B124" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C124">
         <v>6.99</v>
@@ -2466,10 +2501,10 @@
         <v>170</v>
       </c>
       <c r="B125" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C125">
-        <v>8.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -2477,10 +2512,10 @@
         <v>170</v>
       </c>
       <c r="B126" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C126">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -2488,10 +2523,10 @@
         <v>170</v>
       </c>
       <c r="B127" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C127">
-        <v>7.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -2499,7 +2534,7 @@
         <v>170</v>
       </c>
       <c r="B128" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C128">
         <v>7.99</v>
@@ -2510,10 +2545,10 @@
         <v>170</v>
       </c>
       <c r="B129" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C129">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -2521,10 +2556,10 @@
         <v>170</v>
       </c>
       <c r="B130" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C130">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -2532,10 +2567,10 @@
         <v>170</v>
       </c>
       <c r="B131" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C131">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -2543,10 +2578,10 @@
         <v>170</v>
       </c>
       <c r="B132" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C132">
-        <v>3.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -2554,10 +2589,10 @@
         <v>170</v>
       </c>
       <c r="B133" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C133">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
@@ -2565,10 +2600,10 @@
         <v>170</v>
       </c>
       <c r="B134" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C134">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -2576,10 +2611,10 @@
         <v>170</v>
       </c>
       <c r="B135" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C135">
-        <v>5.59</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -2587,10 +2622,10 @@
         <v>170</v>
       </c>
       <c r="B136" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C136">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -2598,10 +2633,10 @@
         <v>170</v>
       </c>
       <c r="B137" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C137">
-        <v>2.59</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -2609,7 +2644,7 @@
         <v>170</v>
       </c>
       <c r="B138" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C138">
         <v>2.59</v>
@@ -2620,7 +2655,7 @@
         <v>170</v>
       </c>
       <c r="B139" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C139">
         <v>2.59</v>
@@ -2631,7 +2666,7 @@
         <v>170</v>
       </c>
       <c r="B140" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C140">
         <v>2.59</v>
@@ -2642,7 +2677,7 @@
         <v>170</v>
       </c>
       <c r="B141" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C141">
         <v>2.59</v>
@@ -2653,7 +2688,7 @@
         <v>170</v>
       </c>
       <c r="B142" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C142">
         <v>2.59</v>
@@ -2664,7 +2699,7 @@
         <v>170</v>
       </c>
       <c r="B143" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C143">
         <v>2.59</v>
@@ -2675,10 +2710,10 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C144">
-        <v>3.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -2686,7 +2721,7 @@
         <v>170</v>
       </c>
       <c r="B145" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C145">
         <v>2.59</v>
@@ -2697,10 +2732,10 @@
         <v>170</v>
       </c>
       <c r="B146" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C146">
-        <v>2.59</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
@@ -2708,10 +2743,10 @@
         <v>170</v>
       </c>
       <c r="B147" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C147">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
@@ -2719,7 +2754,7 @@
         <v>170</v>
       </c>
       <c r="B148" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C148">
         <v>2.59</v>
@@ -2730,10 +2765,10 @@
         <v>170</v>
       </c>
       <c r="B149" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C149">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
@@ -2741,7 +2776,7 @@
         <v>170</v>
       </c>
       <c r="B150" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C150">
         <v>2.59</v>
@@ -2752,10 +2787,10 @@
         <v>170</v>
       </c>
       <c r="B151" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C151">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
@@ -2763,7 +2798,7 @@
         <v>170</v>
       </c>
       <c r="B152" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C152">
         <v>2.59</v>
@@ -2774,7 +2809,7 @@
         <v>170</v>
       </c>
       <c r="B153" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C153">
         <v>1.99</v>
@@ -2785,10 +2820,10 @@
         <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C154">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
@@ -2796,10 +2831,10 @@
         <v>170</v>
       </c>
       <c r="B155" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C155">
-        <v>3.49</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
@@ -2807,10 +2842,10 @@
         <v>170</v>
       </c>
       <c r="B156" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C156">
-        <v>5.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
@@ -2818,10 +2853,10 @@
         <v>170</v>
       </c>
       <c r="B157" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C157">
-        <v>2.59</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
@@ -2829,10 +2864,10 @@
         <v>170</v>
       </c>
       <c r="B158" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C158">
-        <v>2.59</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -2840,7 +2875,7 @@
         <v>170</v>
       </c>
       <c r="B159" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C159">
         <v>2.59</v>
@@ -2848,24 +2883,24 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B160" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C160">
-        <v>9.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B161" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C161">
-        <v>4.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
@@ -2873,10 +2908,10 @@
         <v>193</v>
       </c>
       <c r="B162" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C162">
-        <v>2.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -2884,7 +2919,7 @@
         <v>193</v>
       </c>
       <c r="B163" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C163">
         <v>4.99</v>
@@ -2895,10 +2930,10 @@
         <v>193</v>
       </c>
       <c r="B164" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C164">
-        <v>4.49</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
@@ -2906,10 +2941,10 @@
         <v>193</v>
       </c>
       <c r="B165" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C165">
-        <v>3.49</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -2917,10 +2952,10 @@
         <v>193</v>
       </c>
       <c r="B166" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C166">
-        <v>2.4900000000000002</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -2928,10 +2963,10 @@
         <v>193</v>
       </c>
       <c r="B167" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C167">
-        <v>3.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -2939,10 +2974,10 @@
         <v>193</v>
       </c>
       <c r="B168" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C168">
-        <v>3.99</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -2950,10 +2985,10 @@
         <v>193</v>
       </c>
       <c r="B169" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C169">
-        <v>4.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -2961,10 +2996,10 @@
         <v>193</v>
       </c>
       <c r="B170" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C170">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -2972,10 +3007,10 @@
         <v>193</v>
       </c>
       <c r="B171" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C171">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
@@ -2983,7 +3018,7 @@
         <v>193</v>
       </c>
       <c r="B172" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C172">
         <v>2.99</v>
@@ -2994,10 +3029,10 @@
         <v>193</v>
       </c>
       <c r="B173" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C173">
-        <v>7.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
@@ -3005,10 +3040,10 @@
         <v>193</v>
       </c>
       <c r="B174" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C174">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
@@ -3016,10 +3051,10 @@
         <v>193</v>
       </c>
       <c r="B175" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C175">
-        <v>1.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
@@ -3027,10 +3062,10 @@
         <v>193</v>
       </c>
       <c r="B176" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C176">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
@@ -3038,10 +3073,10 @@
         <v>193</v>
       </c>
       <c r="B177" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C177">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
@@ -3049,10 +3084,10 @@
         <v>193</v>
       </c>
       <c r="B178" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C178">
-        <v>3.49</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
@@ -3060,10 +3095,10 @@
         <v>193</v>
       </c>
       <c r="B179" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C179">
-        <v>5.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
@@ -3071,10 +3106,10 @@
         <v>193</v>
       </c>
       <c r="B180" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C180">
-        <v>6.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -3082,32 +3117,32 @@
         <v>193</v>
       </c>
       <c r="B181" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C181">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B182" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C182">
-        <v>16.989999999999998</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B183" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C183">
-        <v>18.989999999999998</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
@@ -3115,10 +3150,10 @@
         <v>198</v>
       </c>
       <c r="B184" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C184">
-        <v>20.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
@@ -3126,32 +3161,32 @@
         <v>198</v>
       </c>
       <c r="B185" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C185">
-        <v>16.989999999999998</v>
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B186" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C186">
-        <v>3.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B187" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C187">
-        <v>4.59</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
@@ -3159,7 +3194,7 @@
         <v>205</v>
       </c>
       <c r="B188" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C188">
         <v>3.99</v>
@@ -3170,10 +3205,10 @@
         <v>205</v>
       </c>
       <c r="B189" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C189">
-        <v>2.99</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
@@ -3181,10 +3216,10 @@
         <v>205</v>
       </c>
       <c r="B190" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C190">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
@@ -3192,9 +3227,31 @@
         <v>205</v>
       </c>
       <c r="B191" t="s">
+        <v>202</v>
+      </c>
+      <c r="C191">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B192" t="s">
+        <v>203</v>
+      </c>
+      <c r="C192">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B193" t="s">
         <v>204</v>
       </c>
-      <c r="C191">
+      <c r="C193">
         <v>6.99</v>
       </c>
     </row>

--- a/public/menu.xlsx
+++ b/public/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zia Shams\order-system\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995436AB-2637-4E85-A5F1-437A79F08C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D09010-00CA-44CA-A95C-D52A93E70352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="208">
   <si>
     <t>Category</t>
   </si>
@@ -792,20 +792,20 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1115,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D192"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1769,16 +1769,22 @@
       <c r="A58" s="4" t="s">
         <v>66</v>
       </c>
+      <c r="B58" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58">
+        <v>4.99</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C59">
-        <v>4.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -1786,10 +1792,10 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C60">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -1797,7 +1803,7 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>4.99</v>
@@ -1808,7 +1814,7 @@
         <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C62">
         <v>4.99</v>
@@ -1816,13 +1822,13 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C63">
-        <v>4.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -1830,7 +1836,7 @@
         <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C64">
         <v>3.99</v>
@@ -1841,10 +1847,10 @@
         <v>76</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C65">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -1852,10 +1858,10 @@
         <v>76</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C66">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -1863,7 +1869,7 @@
         <v>76</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67">
         <v>3.99</v>
@@ -1874,7 +1880,7 @@
         <v>76</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68">
         <v>3.99</v>
@@ -1885,10 +1891,10 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C69">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1896,10 +1902,10 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C70">
-        <v>7.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -1907,7 +1913,7 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C71">
         <v>3.99</v>
@@ -1915,13 +1921,13 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B72" t="s">
-        <v>75</v>
-      </c>
-      <c r="C72">
-        <v>3.99</v>
+        <v>85</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" s="7">
+        <v>26.99</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1929,7 +1935,7 @@
         <v>85</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C73" s="7">
         <v>26.99</v>
@@ -1940,10 +1946,10 @@
         <v>85</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C74" s="7">
-        <v>26.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -1951,10 +1957,10 @@
         <v>85</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C75" s="7">
-        <v>16.989999999999998</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -1962,10 +1968,10 @@
         <v>85</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C76" s="7">
-        <v>22.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -1973,10 +1979,10 @@
         <v>85</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C77" s="7">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1984,32 +1990,32 @@
         <v>85</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C78" s="7">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C79" s="7">
+      <c r="B79" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79" s="9">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80">
         <v>6.99</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C80" s="9">
-        <v>6.49</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -2017,10 +2023,10 @@
         <v>94</v>
       </c>
       <c r="B81" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C81">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -2028,7 +2034,7 @@
         <v>94</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C82">
         <v>4.99</v>
@@ -2039,7 +2045,7 @@
         <v>94</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C83">
         <v>4.99</v>
@@ -2050,7 +2056,7 @@
         <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C84">
         <v>4.99</v>
@@ -2061,7 +2067,7 @@
         <v>94</v>
       </c>
       <c r="B85" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C85">
         <v>4.99</v>
@@ -2072,10 +2078,10 @@
         <v>94</v>
       </c>
       <c r="B86" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C86">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -2083,21 +2089,21 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C87">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C88">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -2105,10 +2111,10 @@
         <v>116</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C89">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -2116,10 +2122,10 @@
         <v>116</v>
       </c>
       <c r="B90" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C90">
-        <v>6.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -2127,10 +2133,10 @@
         <v>116</v>
       </c>
       <c r="B91" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C91">
-        <v>9.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -2138,10 +2144,10 @@
         <v>116</v>
       </c>
       <c r="B92" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C92">
-        <v>17.989999999999998</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -2149,10 +2155,10 @@
         <v>116</v>
       </c>
       <c r="B93" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C93">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -2160,10 +2166,10 @@
         <v>116</v>
       </c>
       <c r="B94" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C94">
-        <v>4.99</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -2171,10 +2177,10 @@
         <v>116</v>
       </c>
       <c r="B95" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C95">
-        <v>2.4900000000000002</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -2182,10 +2188,10 @@
         <v>116</v>
       </c>
       <c r="B96" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C96">
-        <v>4.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -2193,10 +2199,10 @@
         <v>116</v>
       </c>
       <c r="B97" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C97">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -2204,10 +2210,10 @@
         <v>116</v>
       </c>
       <c r="B98" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C98">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -2215,10 +2221,10 @@
         <v>116</v>
       </c>
       <c r="B99" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C99">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -2226,10 +2232,10 @@
         <v>116</v>
       </c>
       <c r="B100" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C100">
-        <v>6.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -2237,7 +2243,7 @@
         <v>116</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C101">
         <v>1.99</v>
@@ -2248,7 +2254,7 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C102">
         <v>1.99</v>
@@ -2259,10 +2265,10 @@
         <v>116</v>
       </c>
       <c r="B103" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C103">
-        <v>1.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -2270,10 +2276,10 @@
         <v>116</v>
       </c>
       <c r="B104" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C104">
-        <v>15.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -2281,10 +2287,10 @@
         <v>116</v>
       </c>
       <c r="B105" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C105">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -2292,10 +2298,10 @@
         <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C106">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -2303,21 +2309,21 @@
         <v>116</v>
       </c>
       <c r="B107" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C107">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="B108" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C108">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -2325,7 +2331,7 @@
         <v>131</v>
       </c>
       <c r="B109" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C109">
         <v>4.99</v>
@@ -2336,10 +2342,10 @@
         <v>131</v>
       </c>
       <c r="B110" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C110">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -2347,10 +2353,10 @@
         <v>131</v>
       </c>
       <c r="B111" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C111">
-        <v>5.99</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -2358,10 +2364,10 @@
         <v>131</v>
       </c>
       <c r="B112" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C112">
-        <v>0.69</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -2369,10 +2375,10 @@
         <v>131</v>
       </c>
       <c r="B113" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C113">
-        <v>1.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -2380,10 +2386,10 @@
         <v>131</v>
       </c>
       <c r="B114" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C114">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -2391,10 +2397,10 @@
         <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C115">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -2402,10 +2408,10 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C116">
-        <v>6.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -2413,7 +2419,7 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C117">
         <v>4.49</v>
@@ -2424,7 +2430,7 @@
         <v>131</v>
       </c>
       <c r="B118" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C118">
         <v>4.49</v>
@@ -2435,10 +2441,10 @@
         <v>131</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C119">
-        <v>4.49</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -2446,10 +2452,10 @@
         <v>131</v>
       </c>
       <c r="B120" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C120">
-        <v>4.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -2457,21 +2463,21 @@
         <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C121">
-        <v>3.99</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C122">
-        <v>0.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -2479,7 +2485,7 @@
         <v>170</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C123">
         <v>6.99</v>
@@ -2490,7 +2496,7 @@
         <v>170</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C124">
         <v>6.99</v>
@@ -2501,7 +2507,7 @@
         <v>170</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C125">
         <v>6.99</v>
@@ -2512,10 +2518,10 @@
         <v>170</v>
       </c>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C126">
-        <v>6.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -2523,10 +2529,10 @@
         <v>170</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C127">
-        <v>8.49</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -2534,7 +2540,7 @@
         <v>170</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C128">
         <v>7.99</v>
@@ -2545,7 +2551,7 @@
         <v>170</v>
       </c>
       <c r="B129" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C129">
         <v>7.99</v>
@@ -2556,10 +2562,10 @@
         <v>170</v>
       </c>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C130">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -2567,10 +2573,10 @@
         <v>170</v>
       </c>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C131">
-        <v>6.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -2578,10 +2584,10 @@
         <v>170</v>
       </c>
       <c r="B132" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C132">
-        <v>14.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -2589,7 +2595,7 @@
         <v>170</v>
       </c>
       <c r="B133" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C133">
         <v>3.99</v>
@@ -2600,10 +2606,10 @@
         <v>170</v>
       </c>
       <c r="B134" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C134">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -2611,7 +2617,7 @@
         <v>170</v>
       </c>
       <c r="B135" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C135">
         <v>2.99</v>
@@ -2622,10 +2628,10 @@
         <v>170</v>
       </c>
       <c r="B136" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C136">
-        <v>2.99</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -2633,10 +2639,10 @@
         <v>170</v>
       </c>
       <c r="B137" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C137">
-        <v>5.59</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -2644,7 +2650,7 @@
         <v>170</v>
       </c>
       <c r="B138" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C138">
         <v>2.59</v>
@@ -2655,7 +2661,7 @@
         <v>170</v>
       </c>
       <c r="B139" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C139">
         <v>2.59</v>
@@ -2666,7 +2672,7 @@
         <v>170</v>
       </c>
       <c r="B140" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C140">
         <v>2.59</v>
@@ -2677,7 +2683,7 @@
         <v>170</v>
       </c>
       <c r="B141" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C141">
         <v>2.59</v>
@@ -2699,7 +2705,7 @@
         <v>170</v>
       </c>
       <c r="B143" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C143">
         <v>2.59</v>
@@ -2710,7 +2716,7 @@
         <v>170</v>
       </c>
       <c r="B144" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C144">
         <v>2.59</v>
@@ -2721,10 +2727,10 @@
         <v>170</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C145">
-        <v>2.59</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -2732,10 +2738,10 @@
         <v>170</v>
       </c>
       <c r="B146" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C146">
-        <v>3.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
@@ -2743,7 +2749,7 @@
         <v>170</v>
       </c>
       <c r="B147" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C147">
         <v>2.59</v>
@@ -2754,10 +2760,10 @@
         <v>170</v>
       </c>
       <c r="B148" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C148">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
@@ -2765,10 +2771,10 @@
         <v>170</v>
       </c>
       <c r="B149" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C149">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
@@ -2776,7 +2782,7 @@
         <v>170</v>
       </c>
       <c r="B150" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C150">
         <v>2.59</v>
@@ -2787,7 +2793,7 @@
         <v>170</v>
       </c>
       <c r="B151" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C151">
         <v>2.59</v>
@@ -2798,10 +2804,10 @@
         <v>170</v>
       </c>
       <c r="B152" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C152">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
@@ -2809,10 +2815,10 @@
         <v>170</v>
       </c>
       <c r="B153" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C153">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
@@ -2820,10 +2826,10 @@
         <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C154">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
@@ -2831,7 +2837,7 @@
         <v>170</v>
       </c>
       <c r="B155" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C155">
         <v>1.99</v>
@@ -2842,10 +2848,10 @@
         <v>170</v>
       </c>
       <c r="B156" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C156">
-        <v>1.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
@@ -2853,10 +2859,10 @@
         <v>170</v>
       </c>
       <c r="B157" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C157">
-        <v>3.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
@@ -2864,10 +2870,10 @@
         <v>170</v>
       </c>
       <c r="B158" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C158">
-        <v>5.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -2875,7 +2881,7 @@
         <v>170</v>
       </c>
       <c r="B159" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C159">
         <v>2.59</v>
@@ -2886,7 +2892,7 @@
         <v>170</v>
       </c>
       <c r="B160" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C160">
         <v>2.59</v>
@@ -2894,13 +2900,13 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B161" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C161">
-        <v>2.59</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
@@ -2908,10 +2914,10 @@
         <v>193</v>
       </c>
       <c r="B162" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C162">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -2919,10 +2925,10 @@
         <v>193</v>
       </c>
       <c r="B163" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C163">
-        <v>4.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
@@ -2930,10 +2936,10 @@
         <v>193</v>
       </c>
       <c r="B164" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C164">
-        <v>2.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
@@ -2941,10 +2947,10 @@
         <v>193</v>
       </c>
       <c r="B165" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C165">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -2952,10 +2958,10 @@
         <v>193</v>
       </c>
       <c r="B166" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C166">
-        <v>4.49</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -2963,10 +2969,10 @@
         <v>193</v>
       </c>
       <c r="B167" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C167">
-        <v>3.49</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -2974,10 +2980,10 @@
         <v>193</v>
       </c>
       <c r="B168" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C168">
-        <v>2.4900000000000002</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -2985,7 +2991,7 @@
         <v>193</v>
       </c>
       <c r="B169" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C169">
         <v>3.99</v>
@@ -2996,10 +3002,10 @@
         <v>193</v>
       </c>
       <c r="B170" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C170">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -3007,10 +3013,10 @@
         <v>193</v>
       </c>
       <c r="B171" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C171">
-        <v>4.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
@@ -3018,10 +3024,10 @@
         <v>193</v>
       </c>
       <c r="B172" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C172">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
@@ -3029,10 +3035,10 @@
         <v>193</v>
       </c>
       <c r="B173" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C173">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
@@ -3040,10 +3046,10 @@
         <v>193</v>
       </c>
       <c r="B174" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C174">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
@@ -3051,10 +3057,10 @@
         <v>193</v>
       </c>
       <c r="B175" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C175">
-        <v>7.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
@@ -3062,7 +3068,7 @@
         <v>193</v>
       </c>
       <c r="B176" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C176">
         <v>1.99</v>
@@ -3073,10 +3079,10 @@
         <v>193</v>
       </c>
       <c r="B177" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C177">
-        <v>1.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
@@ -3084,7 +3090,7 @@
         <v>193</v>
       </c>
       <c r="B178" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C178">
         <v>4.49</v>
@@ -3095,10 +3101,10 @@
         <v>193</v>
       </c>
       <c r="B179" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C179">
-        <v>4.49</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
@@ -3106,10 +3112,10 @@
         <v>193</v>
       </c>
       <c r="B180" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C180">
-        <v>3.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -3117,10 +3123,10 @@
         <v>193</v>
       </c>
       <c r="B181" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C181">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
@@ -3128,21 +3134,21 @@
         <v>193</v>
       </c>
       <c r="B182" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C182">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B183" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C183">
-        <v>4.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
@@ -3150,10 +3156,10 @@
         <v>198</v>
       </c>
       <c r="B184" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C184">
-        <v>16.989999999999998</v>
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
@@ -3161,10 +3167,10 @@
         <v>198</v>
       </c>
       <c r="B185" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C185">
-        <v>18.989999999999998</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
@@ -3172,21 +3178,21 @@
         <v>198</v>
       </c>
       <c r="B186" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C186">
-        <v>20.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B187" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C187">
-        <v>16.989999999999998</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
@@ -3194,10 +3200,10 @@
         <v>205</v>
       </c>
       <c r="B188" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C188">
-        <v>3.99</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
@@ -3205,10 +3211,10 @@
         <v>205</v>
       </c>
       <c r="B189" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C189">
-        <v>4.59</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
@@ -3216,10 +3222,10 @@
         <v>205</v>
       </c>
       <c r="B190" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C190">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
@@ -3227,10 +3233,10 @@
         <v>205</v>
       </c>
       <c r="B191" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C191">
-        <v>2.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
@@ -3238,20 +3244,9 @@
         <v>205</v>
       </c>
       <c r="B192" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C192">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B193" t="s">
-        <v>204</v>
-      </c>
-      <c r="C193">
         <v>6.99</v>
       </c>
     </row>

--- a/public/menu.xlsx
+++ b/public/menu.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zia Shams\order-system\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zia Shams\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D09010-00CA-44CA-A95C-D52A93E70352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE21D2D9-A3A6-4047-8B04-0A1C3D5B4798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="197">
   <si>
     <t>Category</t>
   </si>
@@ -151,15 +151,9 @@
     <t>Mutton (Goat) - Approx. 2lb Pack - Local - Price is per LB</t>
   </si>
   <si>
-    <t>Local Lamb (2lb Pack) - Price is per LB</t>
-  </si>
-  <si>
     <t>Lamb Leg - (whole) - Local - Price is per LB</t>
   </si>
   <si>
-    <t>Lamb Chop - Price is per LB</t>
-  </si>
-  <si>
     <t>Nona Ilish (whole fish)</t>
   </si>
   <si>
@@ -178,9 +172,6 @@
     <t>Faisha Shidol 150gm</t>
   </si>
   <si>
-    <t>Premium Sweets Morog Pulao</t>
-  </si>
-  <si>
     <t>Premium sweets Brain Masala</t>
   </si>
   <si>
@@ -232,12 +223,6 @@
     <t>Frozen Chui Jhal</t>
   </si>
   <si>
-    <t>Lal Shak</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
     <t>Frozen Jolpai</t>
   </si>
   <si>
@@ -247,9 +232,6 @@
     <t>Frozen Satkora</t>
   </si>
   <si>
-    <t>Kochur Loti</t>
-  </si>
-  <si>
     <t>Frozen Vegetables</t>
   </si>
   <si>
@@ -313,9 +295,6 @@
     <t>Bombay Laccha Semai 350gm</t>
   </si>
   <si>
-    <t>Ispahani/Taza Tea 400gm</t>
-  </si>
-  <si>
     <t>Nido Milk Powder 2500gm</t>
   </si>
   <si>
@@ -355,9 +334,6 @@
     <t>Food Color (Yellow) (25gm)</t>
   </si>
   <si>
-    <t>Khejur Gur 1KG</t>
-  </si>
-  <si>
     <t>Radhuni Kashundi</t>
   </si>
   <si>
@@ -379,9 +355,6 @@
     <t>Banaful Plain Toast</t>
   </si>
   <si>
-    <t>Olympia Ghee Toast</t>
-  </si>
-  <si>
     <t>Kishwan Mango Bar</t>
   </si>
   <si>
@@ -427,9 +400,6 @@
     <t>Ginger Garlic Paste (750ml)</t>
   </si>
   <si>
-    <t>RADHUNI CHILI POWDER (400GM)</t>
-  </si>
-  <si>
     <t>RADHUNI CHILI POWDER (500GM)</t>
   </si>
   <si>
@@ -442,9 +412,6 @@
     <t>CORIANDER 500GM - ধনে গুড়া</t>
   </si>
   <si>
-    <t>CUMIN POWDER 200GM - জিরা গুড়া</t>
-  </si>
-  <si>
     <t>CUMIN POWDER 500GM - জিরা গুড়া</t>
   </si>
   <si>
@@ -640,10 +607,10 @@
     <t>Desert Ingredients</t>
   </si>
   <si>
-    <t>Specials</t>
-  </si>
-  <si>
-    <t>Sale Price</t>
+    <t>Taza Tea 400gm</t>
+  </si>
+  <si>
+    <t>Khejur Gur 500gm</t>
   </si>
 </sst>
 </file>
@@ -666,6 +633,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -682,7 +650,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -764,24 +732,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -806,13 +761,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1115,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D192"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1123,7 +1071,7 @@
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,185 +1081,170 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" s="12">
-        <v>10.99</v>
-      </c>
-      <c r="D2" s="12">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="12">
-        <v>84.99</v>
-      </c>
-      <c r="D3" s="12">
-        <v>79.989999999999995</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>206</v>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>42.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3">
-        <v>13.99</v>
-      </c>
-      <c r="D4" s="12">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
-        <v>206</v>
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3">
-        <v>5.99</v>
-      </c>
-      <c r="D5" s="12">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="11">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3">
+        <v>54.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3">
-        <v>42.99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>48.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3">
-        <v>54.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3">
-        <v>48.99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3">
-        <v>37.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C13" s="3">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C14" s="3">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3">
-        <v>13.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1319,10 +1252,10 @@
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3">
-        <v>16.989999999999998</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -1330,10 +1263,10 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C18" s="3">
-        <v>17.989999999999998</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -1341,10 +1274,10 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3">
-        <v>8.99</v>
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1352,7 +1285,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3">
         <v>5.99</v>
@@ -1363,10 +1296,10 @@
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C21" s="3">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1374,10 +1307,10 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C22" s="3">
-        <v>18.989999999999998</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1385,10 +1318,10 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C23" s="3">
-        <v>5.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -1396,10 +1329,10 @@
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C24" s="3">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -1407,10 +1340,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C25" s="3">
-        <v>11.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -1418,10 +1351,10 @@
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C26" s="3">
-        <v>15.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -1429,7 +1362,7 @@
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C27" s="3">
         <v>12.99</v>
@@ -1437,35 +1370,35 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C28" s="3">
-        <v>12.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C29" s="3">
-        <v>12.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C30" s="3">
-        <v>12.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -1473,10 +1406,10 @@
         <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C31" s="3">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -1484,10 +1417,10 @@
         <v>7</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C32" s="3">
-        <v>10.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -1495,7 +1428,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C33" s="3">
         <v>6.99</v>
@@ -1506,10 +1439,10 @@
         <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C34" s="3">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -1517,7 +1450,7 @@
         <v>7</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C35" s="3">
         <v>6.99</v>
@@ -1528,10 +1461,10 @@
         <v>7</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C36" s="3">
-        <v>6.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1539,10 +1472,10 @@
         <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C37" s="3">
-        <v>4.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1550,10 +1483,10 @@
         <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3">
-        <v>6.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1561,10 +1494,10 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C39" s="3">
-        <v>15.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -1572,84 +1505,84 @@
         <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C40" s="3">
-        <v>15.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C41" s="3">
-        <v>34.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C42" s="3">
-        <v>13.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C43" s="3">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C44" s="3">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C45" s="3">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C46" s="3">
-        <v>16.989999999999998</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C47" s="3">
         <v>6.49</v>
@@ -1657,175 +1590,175 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C48" s="3">
-        <v>5.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C49" s="3">
-        <v>5.99</v>
+        <v>56</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="5">
+        <v>6.49</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C50" s="3">
-        <v>5.99</v>
+        <v>56</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="5">
+        <v>6.49</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" t="s">
         <v>59</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="3">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="3">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="3">
-        <v>6.49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="3">
-        <v>6.49</v>
+      <c r="C54">
+        <v>11.99</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" s="5">
-        <v>6.49</v>
+      <c r="A55" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55">
+        <v>4.99</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" s="5">
-        <v>6.49</v>
+      <c r="A56" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56">
+        <v>4.99</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>59</v>
+      <c r="A57" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C57">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C58">
-        <v>4.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C59">
-        <v>11.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60" t="s">
         <v>66</v>
       </c>
-      <c r="B60" t="s">
-        <v>63</v>
-      </c>
       <c r="C60">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C61">
-        <v>4.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C62">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C63">
         <v>3.99</v>
@@ -1833,315 +1766,315 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64" t="s">
-        <v>68</v>
-      </c>
-      <c r="C64">
-        <v>3.99</v>
+        <v>79</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="7">
+        <v>26.99</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B65" t="s">
-        <v>69</v>
-      </c>
-      <c r="C65">
-        <v>5.99</v>
+        <v>79</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C65" s="7">
+        <v>26.99</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B66" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66">
-        <v>3.99</v>
+        <v>79</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" s="7">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B67" t="s">
-        <v>71</v>
-      </c>
-      <c r="C67">
-        <v>3.99</v>
+        <v>79</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67" s="7">
+        <v>22.99</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B68" t="s">
-        <v>72</v>
-      </c>
-      <c r="C68">
-        <v>3.99</v>
+        <v>79</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" s="7">
+        <v>6.99</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B69" t="s">
-        <v>73</v>
-      </c>
-      <c r="C69">
-        <v>7.99</v>
+      <c r="C69" s="7">
+        <v>8.99</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" t="s">
-        <v>74</v>
-      </c>
-      <c r="C70">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" s="7">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B71" t="s">
-        <v>75</v>
-      </c>
-      <c r="C71">
-        <v>3.99</v>
+        <v>79</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71" s="9">
+        <v>6.49</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C72" s="7">
-        <v>26.99</v>
+        <v>88</v>
+      </c>
+      <c r="B72" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72">
+        <v>6.99</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C73" s="7">
-        <v>26.99</v>
+        <v>88</v>
+      </c>
+      <c r="B73" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73">
+        <v>4.99</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C74" s="7">
-        <v>16.989999999999998</v>
+        <v>88</v>
+      </c>
+      <c r="B74" t="s">
+        <v>82</v>
+      </c>
+      <c r="C74">
+        <v>4.99</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C75" s="7">
-        <v>22.99</v>
+        <v>88</v>
+      </c>
+      <c r="B75" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75">
+        <v>4.99</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C76" s="7">
-        <v>6.99</v>
+        <v>88</v>
+      </c>
+      <c r="B76" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76">
+        <v>4.99</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77" t="s">
         <v>85</v>
       </c>
-      <c r="B77" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C77" s="7">
-        <v>8.99</v>
+      <c r="C77">
+        <v>4.99</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C78" s="7">
+        <v>88</v>
+      </c>
+      <c r="B78" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79" t="s">
+        <v>87</v>
+      </c>
+      <c r="C79">
         <v>6.99</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C79" s="9">
-        <v>6.49</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C80">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C81">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>195</v>
       </c>
       <c r="C82">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C83">
-        <v>4.99</v>
+        <v>84.99</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B84" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C84">
-        <v>4.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C85">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B86" t="s">
         <v>94</v>
       </c>
-      <c r="B86" t="s">
-        <v>92</v>
-      </c>
       <c r="C86">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C87">
-        <v>6.99</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B88" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C88">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B89" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C89">
-        <v>6.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B90" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C90">
-        <v>9.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B91" t="s">
         <v>99</v>
       </c>
       <c r="C91">
-        <v>17.989999999999998</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B92" t="s">
         <v>100</v>
@@ -2152,54 +2085,54 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B93" t="s">
         <v>101</v>
       </c>
       <c r="C93">
-        <v>4.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B94" t="s">
         <v>102</v>
       </c>
       <c r="C94">
-        <v>2.4900000000000002</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B95" t="s">
         <v>103</v>
       </c>
       <c r="C95">
-        <v>4.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B96" t="s">
-        <v>104</v>
+        <v>196</v>
       </c>
       <c r="C96">
-        <v>1.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C97">
         <v>2.99</v>
@@ -2207,106 +2140,106 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C98">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C99">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C100">
-        <v>1.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B101" t="s">
         <v>109</v>
       </c>
       <c r="C101">
-        <v>1.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B102" t="s">
         <v>110</v>
       </c>
       <c r="C102">
-        <v>1.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B103" t="s">
         <v>111</v>
       </c>
       <c r="C103">
-        <v>15.99</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B104" t="s">
         <v>112</v>
       </c>
       <c r="C104">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B105" t="s">
         <v>113</v>
       </c>
       <c r="C105">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B106" t="s">
         <v>114</v>
       </c>
       <c r="C106">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B107" t="s">
         <v>115</v>
@@ -2317,84 +2250,84 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C108">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B109" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C109">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B110" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C110">
-        <v>5.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B111" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C111">
-        <v>0.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C112">
-        <v>1.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B113" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C113">
-        <v>3.99</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="B114" t="s">
         <v>123</v>
       </c>
       <c r="C114">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="B115" t="s">
         <v>124</v>
@@ -2405,241 +2338,241 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="B116" t="s">
         <v>125</v>
       </c>
       <c r="C116">
-        <v>4.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="B117" t="s">
         <v>126</v>
       </c>
       <c r="C117">
-        <v>4.49</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="B118" t="s">
         <v>127</v>
       </c>
       <c r="C118">
-        <v>4.49</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="B119" t="s">
         <v>128</v>
       </c>
       <c r="C119">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="B120" t="s">
         <v>129</v>
       </c>
       <c r="C120">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="B121" t="s">
         <v>130</v>
       </c>
       <c r="C121">
-        <v>0.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B122" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C122">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B123" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C123">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B124" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C124">
-        <v>6.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C125">
-        <v>6.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B126" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C126">
-        <v>8.49</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C127">
-        <v>7.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B128" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C128">
-        <v>7.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B129" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C129">
-        <v>7.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B130" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C130">
-        <v>6.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B131" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C131">
-        <v>14.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B132" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C132">
-        <v>3.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B133" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C133">
-        <v>3.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B134" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C134">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B135" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C135">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B136" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C136">
-        <v>5.59</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B137" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C137">
         <v>2.59</v>
@@ -2647,21 +2580,21 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B138" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C138">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B139" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C139">
         <v>2.59</v>
@@ -2669,10 +2602,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B140" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C140">
         <v>2.59</v>
@@ -2680,10 +2613,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B141" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C141">
         <v>2.59</v>
@@ -2691,21 +2624,21 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C142">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C143">
         <v>2.59</v>
@@ -2713,65 +2646,65 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C144">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B145" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C145">
-        <v>3.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B146" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C146">
-        <v>2.59</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B147" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C147">
-        <v>2.59</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B148" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C148">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C149">
         <v>2.59</v>
@@ -2779,10 +2712,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B150" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C150">
         <v>2.59</v>
@@ -2790,62 +2723,62 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B151" t="s">
         <v>160</v>
       </c>
       <c r="C151">
-        <v>2.59</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B152" t="s">
         <v>161</v>
       </c>
       <c r="C152">
-        <v>1.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B153" t="s">
         <v>162</v>
       </c>
       <c r="C153">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B154" t="s">
         <v>163</v>
       </c>
       <c r="C154">
-        <v>1.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B155" t="s">
         <v>164</v>
       </c>
       <c r="C155">
-        <v>1.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B156" t="s">
         <v>165</v>
@@ -2856,76 +2789,76 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B157" t="s">
         <v>166</v>
       </c>
       <c r="C157">
-        <v>5.99</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B158" t="s">
         <v>167</v>
       </c>
       <c r="C158">
-        <v>2.59</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B159" t="s">
         <v>168</v>
       </c>
       <c r="C159">
-        <v>2.59</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B160" t="s">
         <v>169</v>
       </c>
       <c r="C160">
-        <v>2.59</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B161" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C161">
-        <v>9.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B162" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C162">
-        <v>4.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B163" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C163">
         <v>2.99</v>
@@ -2933,320 +2866,210 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B164" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C164">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B165" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C165">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B166" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C166">
-        <v>3.49</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B167" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C167">
-        <v>2.4900000000000002</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B168" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C168">
-        <v>3.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B169" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C169">
-        <v>3.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B170" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C170">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B171" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C171">
-        <v>2.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B172" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C172">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B173" t="s">
         <v>183</v>
       </c>
       <c r="C173">
-        <v>2.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B174" t="s">
         <v>184</v>
       </c>
       <c r="C174">
-        <v>7.99</v>
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B175" t="s">
         <v>185</v>
       </c>
       <c r="C175">
-        <v>1.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B176" t="s">
         <v>186</v>
       </c>
       <c r="C176">
-        <v>1.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B177" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C177">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B178" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C178">
-        <v>4.49</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B179" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C179">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B180" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C180">
-        <v>5.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B181" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C181">
-        <v>6.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B182" t="s">
         <v>193</v>
       </c>
-      <c r="B182" t="s">
-        <v>192</v>
-      </c>
       <c r="C182">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A183" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B183" t="s">
-        <v>194</v>
-      </c>
-      <c r="C183">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A184" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B184" t="s">
-        <v>195</v>
-      </c>
-      <c r="C184">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A185" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B185" t="s">
-        <v>196</v>
-      </c>
-      <c r="C185">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A186" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B186" t="s">
-        <v>197</v>
-      </c>
-      <c r="C186">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A187" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B187" t="s">
-        <v>199</v>
-      </c>
-      <c r="C187">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B188" t="s">
-        <v>200</v>
-      </c>
-      <c r="C188">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B189" t="s">
-        <v>201</v>
-      </c>
-      <c r="C189">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B190" t="s">
-        <v>202</v>
-      </c>
-      <c r="C190">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B191" t="s">
-        <v>203</v>
-      </c>
-      <c r="C191">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B192" t="s">
-        <v>204</v>
-      </c>
-      <c r="C192">
         <v>6.99</v>
       </c>
     </row>

--- a/public/menu.xlsx
+++ b/public/menu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zia Shams\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE21D2D9-A3A6-4047-8B04-0A1C3D5B4798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5113EF07-FDFD-4472-A37A-84F14CBB8DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="204">
   <si>
     <t>Category</t>
   </si>
@@ -611,6 +611,27 @@
   </si>
   <si>
     <t>Khejur Gur 500gm</t>
+  </si>
+  <si>
+    <t>Flyer</t>
+  </si>
+  <si>
+    <t>Sale Price</t>
+  </si>
+  <si>
+    <t>Muktagasar Monda</t>
+  </si>
+  <si>
+    <t>Maggi Thai Soup</t>
+  </si>
+  <si>
+    <t>Radhuni Kacchi Biriyani Masala (x 5 Pieces)</t>
+  </si>
+  <si>
+    <t>Mrigel Fish (3KG) - Cut &amp; Descaled (1x Piece)</t>
+  </si>
+  <si>
+    <t>Red Chicken (2x Pieces)</t>
   </si>
 </sst>
 </file>
@@ -736,7 +757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -761,6 +782,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1063,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C182"/>
+  <dimension ref="A1:D187"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1071,7 +1095,7 @@
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1081,170 +1105,188 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>197</v>
+      </c>
+      <c r="B2" t="s">
+        <v>201</v>
       </c>
       <c r="C2" s="3">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12.95</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>202</v>
       </c>
       <c r="C3" s="3">
+        <v>49.99</v>
+      </c>
+      <c r="D3">
         <v>42.99</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>197</v>
+      </c>
+      <c r="B4" t="s">
+        <v>203</v>
       </c>
       <c r="C4" s="3">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>31.98</v>
+      </c>
+      <c r="D4">
+        <v>27.98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>197</v>
+      </c>
+      <c r="B5" t="s">
+        <v>199</v>
       </c>
       <c r="C5" s="3">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="D5">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>197</v>
+      </c>
+      <c r="B6" t="s">
+        <v>200</v>
       </c>
       <c r="C6" s="3">
-        <v>54.99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>23.88</v>
+      </c>
+      <c r="D6">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3">
-        <v>48.99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3">
-        <v>37.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>42.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>54.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>48.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3">
-        <v>5.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1252,7 +1294,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3">
         <v>13.99</v>
@@ -1263,10 +1305,10 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C18" s="3">
-        <v>6.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -1274,10 +1316,10 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C19" s="3">
-        <v>18.989999999999998</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1285,10 +1327,10 @@
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C20" s="3">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1296,7 +1338,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C21" s="3">
         <v>5.99</v>
@@ -1307,10 +1349,10 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3">
-        <v>11.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1318,10 +1360,10 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C23" s="3">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -1329,10 +1371,10 @@
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C24" s="3">
-        <v>12.99</v>
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -1340,10 +1382,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C25" s="3">
-        <v>12.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -1351,10 +1393,10 @@
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C26" s="3">
-        <v>12.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -1362,65 +1404,65 @@
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C27" s="3">
-        <v>12.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C28" s="3">
-        <v>7.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C29" s="3">
-        <v>10.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C30" s="3">
-        <v>6.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C31" s="3">
-        <v>6.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C32" s="3">
-        <v>6.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -1428,10 +1470,10 @@
         <v>7</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C33" s="3">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -1439,10 +1481,10 @@
         <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C34" s="3">
-        <v>4.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -1450,7 +1492,7 @@
         <v>7</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C35" s="3">
         <v>6.99</v>
@@ -1461,10 +1503,10 @@
         <v>7</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C36" s="3">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1472,10 +1514,10 @@
         <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C37" s="3">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1483,10 +1525,10 @@
         <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C38" s="3">
-        <v>34.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1494,10 +1536,10 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C39" s="3">
-        <v>13.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -1505,84 +1547,84 @@
         <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C40" s="3">
-        <v>11.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C41" s="3">
-        <v>16.989999999999998</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C42" s="3">
-        <v>6.49</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C43" s="3">
-        <v>5.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C44" s="3">
-        <v>5.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C45" s="3">
-        <v>5.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C46" s="3">
-        <v>15.99</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C47" s="3">
         <v>6.49</v>
@@ -1590,101 +1632,101 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C48" s="3">
-        <v>6.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="5">
-        <v>6.49</v>
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="3">
+        <v>5.99</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C50" s="5">
-        <v>6.49</v>
+        <v>47</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="3">
+        <v>5.99</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" s="3">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="3">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="3">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="5">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" s="5">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" t="s">
         <v>55</v>
       </c>
-      <c r="C51">
+      <c r="C56">
         <v>3.99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B53" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>4.99</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -1692,65 +1734,65 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C57">
-        <v>4.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C58">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C59">
-        <v>3.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C60">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C61">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C62">
-        <v>7.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -1758,7 +1800,7 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C63">
         <v>3.99</v>
@@ -1766,57 +1808,57 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C64" s="7">
-        <v>26.99</v>
+        <v>70</v>
+      </c>
+      <c r="B64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64">
+        <v>3.99</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C65" s="7">
-        <v>26.99</v>
+        <v>70</v>
+      </c>
+      <c r="B65" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65">
+        <v>5.99</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C66" s="7">
-        <v>16.989999999999998</v>
+        <v>70</v>
+      </c>
+      <c r="B66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C66">
+        <v>3.99</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C67" s="7">
-        <v>22.99</v>
+        <v>70</v>
+      </c>
+      <c r="B67" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67">
+        <v>7.99</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C68" s="7">
-        <v>6.99</v>
+        <v>70</v>
+      </c>
+      <c r="B68" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68">
+        <v>3.99</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -1824,10 +1866,10 @@
         <v>79</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C69" s="7">
-        <v>8.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1835,76 +1877,76 @@
         <v>79</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C70" s="7">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B71" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C71" s="9">
-        <v>6.49</v>
+      <c r="B71" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="7">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B72" t="s">
-        <v>80</v>
-      </c>
-      <c r="C72">
-        <v>6.99</v>
+        <v>79</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C72" s="7">
+        <v>22.99</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B73" t="s">
-        <v>81</v>
-      </c>
-      <c r="C73">
-        <v>4.99</v>
+        <v>79</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" s="7">
+        <v>6.99</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B74" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74">
-        <v>4.99</v>
+        <v>79</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C74" s="7">
+        <v>8.99</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B75" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C75" s="7">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B76" t="s">
-        <v>84</v>
-      </c>
-      <c r="C76">
-        <v>4.99</v>
+        <v>79</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" s="9">
+        <v>6.49</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -1912,10 +1954,10 @@
         <v>88</v>
       </c>
       <c r="B77" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C77">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1923,10 +1965,10 @@
         <v>88</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C78">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -1934,65 +1976,65 @@
         <v>88</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C79">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C80">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C81">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="C82">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C83">
-        <v>84.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C84">
-        <v>17.989999999999998</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -2000,10 +2042,10 @@
         <v>108</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C85">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -2011,10 +2053,10 @@
         <v>108</v>
       </c>
       <c r="B86" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C86">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -2022,10 +2064,10 @@
         <v>108</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="C87">
-        <v>2.4900000000000002</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -2033,10 +2075,10 @@
         <v>108</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C88">
-        <v>4.99</v>
+        <v>84.99</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -2044,10 +2086,10 @@
         <v>108</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C89">
-        <v>1.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -2055,10 +2097,10 @@
         <v>108</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C90">
-        <v>2.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -2066,10 +2108,10 @@
         <v>108</v>
       </c>
       <c r="B91" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C91">
-        <v>7.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -2077,10 +2119,10 @@
         <v>108</v>
       </c>
       <c r="B92" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C92">
-        <v>6.99</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -2088,10 +2130,10 @@
         <v>108</v>
       </c>
       <c r="B93" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C93">
-        <v>1.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -2099,7 +2141,7 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C94">
         <v>1.99</v>
@@ -2110,10 +2152,10 @@
         <v>108</v>
       </c>
       <c r="B95" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C95">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -2121,10 +2163,10 @@
         <v>108</v>
       </c>
       <c r="B96" t="s">
-        <v>196</v>
+        <v>99</v>
       </c>
       <c r="C96">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -2132,10 +2174,10 @@
         <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C97">
-        <v>2.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -2143,10 +2185,10 @@
         <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C98">
-        <v>5.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -2154,10 +2196,10 @@
         <v>108</v>
       </c>
       <c r="B99" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C99">
-        <v>3.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -2165,65 +2207,65 @@
         <v>108</v>
       </c>
       <c r="B100" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C100">
-        <v>6.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="C101">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B102" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C102">
-        <v>4.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C103">
-        <v>0.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B104" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C104">
-        <v>1.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B105" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C105">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -2231,10 +2273,10 @@
         <v>122</v>
       </c>
       <c r="B106" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C106">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -2242,10 +2284,10 @@
         <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C107">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
@@ -2253,10 +2295,10 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C108">
-        <v>4.49</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -2264,10 +2306,10 @@
         <v>122</v>
       </c>
       <c r="B109" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C109">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -2275,10 +2317,10 @@
         <v>122</v>
       </c>
       <c r="B110" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C110">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -2286,10 +2328,10 @@
         <v>122</v>
       </c>
       <c r="B111" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C111">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -2297,10 +2339,10 @@
         <v>122</v>
       </c>
       <c r="B112" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C112">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -2308,65 +2350,65 @@
         <v>122</v>
       </c>
       <c r="B113" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C113">
-        <v>0.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="B114" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C114">
-        <v>6.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C115">
-        <v>6.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="B116" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C116">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C117">
-        <v>8.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C118">
-        <v>7.99</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -2374,10 +2416,10 @@
         <v>159</v>
       </c>
       <c r="B119" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C119">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -2385,10 +2427,10 @@
         <v>159</v>
       </c>
       <c r="B120" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C120">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -2396,10 +2438,10 @@
         <v>159</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C121">
-        <v>14.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -2407,10 +2449,10 @@
         <v>159</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C122">
-        <v>3.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -2418,10 +2460,10 @@
         <v>159</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C123">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -2429,10 +2471,10 @@
         <v>159</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C124">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -2440,10 +2482,10 @@
         <v>159</v>
       </c>
       <c r="B125" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C125">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -2451,10 +2493,10 @@
         <v>159</v>
       </c>
       <c r="B126" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C126">
-        <v>5.59</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -2462,10 +2504,10 @@
         <v>159</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C127">
-        <v>2.59</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -2473,10 +2515,10 @@
         <v>159</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C128">
-        <v>2.59</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
@@ -2484,10 +2526,10 @@
         <v>159</v>
       </c>
       <c r="B129" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C129">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -2495,10 +2537,10 @@
         <v>159</v>
       </c>
       <c r="B130" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C130">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -2506,10 +2548,10 @@
         <v>159</v>
       </c>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C131">
-        <v>2.59</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -2517,7 +2559,7 @@
         <v>159</v>
       </c>
       <c r="B132" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C132">
         <v>2.59</v>
@@ -2528,7 +2570,7 @@
         <v>159</v>
       </c>
       <c r="B133" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C133">
         <v>2.59</v>
@@ -2539,7 +2581,7 @@
         <v>159</v>
       </c>
       <c r="B134" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C134">
         <v>2.59</v>
@@ -2550,10 +2592,10 @@
         <v>159</v>
       </c>
       <c r="B135" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C135">
-        <v>3.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -2561,7 +2603,7 @@
         <v>159</v>
       </c>
       <c r="B136" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C136">
         <v>2.59</v>
@@ -2572,7 +2614,7 @@
         <v>159</v>
       </c>
       <c r="B137" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C137">
         <v>2.59</v>
@@ -2583,10 +2625,10 @@
         <v>159</v>
       </c>
       <c r="B138" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C138">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -2594,7 +2636,7 @@
         <v>159</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C139">
         <v>2.59</v>
@@ -2605,10 +2647,10 @@
         <v>159</v>
       </c>
       <c r="B140" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C140">
-        <v>2.59</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
@@ -2616,7 +2658,7 @@
         <v>159</v>
       </c>
       <c r="B141" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C141">
         <v>2.59</v>
@@ -2627,10 +2669,10 @@
         <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C142">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
@@ -2638,10 +2680,10 @@
         <v>159</v>
       </c>
       <c r="B143" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C143">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
@@ -2649,10 +2691,10 @@
         <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C144">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -2660,10 +2702,10 @@
         <v>159</v>
       </c>
       <c r="B145" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C145">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -2671,10 +2713,10 @@
         <v>159</v>
       </c>
       <c r="B146" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C146">
-        <v>3.49</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
@@ -2682,10 +2724,10 @@
         <v>159</v>
       </c>
       <c r="B147" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C147">
-        <v>5.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
@@ -2693,7 +2735,7 @@
         <v>159</v>
       </c>
       <c r="B148" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C148">
         <v>2.59</v>
@@ -2704,10 +2746,10 @@
         <v>159</v>
       </c>
       <c r="B149" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C149">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
@@ -2715,65 +2757,65 @@
         <v>159</v>
       </c>
       <c r="B150" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C150">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B151" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C151">
-        <v>9.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C152">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B153" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C153">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C154">
-        <v>4.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B155" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C155">
-        <v>4.49</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
@@ -2781,10 +2823,10 @@
         <v>182</v>
       </c>
       <c r="B156" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C156">
-        <v>3.49</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
@@ -2792,10 +2834,10 @@
         <v>182</v>
       </c>
       <c r="B157" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C157">
-        <v>2.4900000000000002</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
@@ -2803,10 +2845,10 @@
         <v>182</v>
       </c>
       <c r="B158" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C158">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -2814,10 +2856,10 @@
         <v>182</v>
       </c>
       <c r="B159" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C159">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -2825,10 +2867,10 @@
         <v>182</v>
       </c>
       <c r="B160" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C160">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
@@ -2836,10 +2878,10 @@
         <v>182</v>
       </c>
       <c r="B161" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C161">
-        <v>2.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
@@ -2847,10 +2889,10 @@
         <v>182</v>
       </c>
       <c r="B162" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C162">
-        <v>3.99</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -2858,10 +2900,10 @@
         <v>182</v>
       </c>
       <c r="B163" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C163">
-        <v>2.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
@@ -2869,10 +2911,10 @@
         <v>182</v>
       </c>
       <c r="B164" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C164">
-        <v>7.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
@@ -2880,10 +2922,10 @@
         <v>182</v>
       </c>
       <c r="B165" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C165">
-        <v>1.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -2891,10 +2933,10 @@
         <v>182</v>
       </c>
       <c r="B166" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C166">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -2902,10 +2944,10 @@
         <v>182</v>
       </c>
       <c r="B167" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C167">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -2913,10 +2955,10 @@
         <v>182</v>
       </c>
       <c r="B168" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C168">
-        <v>4.49</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -2924,10 +2966,10 @@
         <v>182</v>
       </c>
       <c r="B169" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C169">
-        <v>3.49</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -2935,10 +2977,10 @@
         <v>182</v>
       </c>
       <c r="B170" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C170">
-        <v>5.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -2946,10 +2988,10 @@
         <v>182</v>
       </c>
       <c r="B171" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C171">
-        <v>6.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
@@ -2957,109 +2999,109 @@
         <v>182</v>
       </c>
       <c r="B172" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C172">
-        <v>4.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B173" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C173">
-        <v>16.989999999999998</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B174" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C174">
-        <v>18.989999999999998</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C175">
-        <v>20.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B176" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C176">
-        <v>16.989999999999998</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B177" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C177">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B178" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C178">
-        <v>4.59</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B179" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C179">
-        <v>3.99</v>
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B180" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C180">
-        <v>2.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B181" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C181">
-        <v>3.49</v>
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
@@ -3067,9 +3109,64 @@
         <v>194</v>
       </c>
       <c r="B182" t="s">
+        <v>188</v>
+      </c>
+      <c r="C182">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B183" t="s">
+        <v>189</v>
+      </c>
+      <c r="C183">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B184" t="s">
+        <v>190</v>
+      </c>
+      <c r="C184">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B185" t="s">
+        <v>191</v>
+      </c>
+      <c r="C185">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B186" t="s">
+        <v>192</v>
+      </c>
+      <c r="C186">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B187" t="s">
         <v>193</v>
       </c>
-      <c r="C182">
+      <c r="C187">
         <v>6.99</v>
       </c>
     </row>

--- a/public/menu.xlsx
+++ b/public/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zia Shams\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5113EF07-FDFD-4472-A37A-84F14CBB8DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D2580B-5585-4113-85AA-BAE4F0EFE166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -613,9 +613,6 @@
     <t>Khejur Gur 500gm</t>
   </si>
   <si>
-    <t>Flyer</t>
-  </si>
-  <si>
     <t>Sale Price</t>
   </si>
   <si>
@@ -632,6 +629,9 @@
   </si>
   <si>
     <t>Red Chicken (2x Pieces)</t>
+  </si>
+  <si>
+    <t>Specials</t>
   </si>
 </sst>
 </file>
@@ -1106,15 +1106,15 @@
         <v>2</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3">
         <v>12.95</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C3" s="3">
         <v>49.99</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C4" s="3">
         <v>31.98</v>
@@ -1153,10 +1153,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C5" s="3">
         <v>19.989999999999998</v>
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C6" s="3">
         <v>23.88</v>
